--- a/data/qa/prospect_to_cash/payment.xlsx
+++ b/data/qa/prospect_to_cash/payment.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,126 +426,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X3"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>field</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>intent</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sub_intent</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>canonical_question</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>answer</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>keywords</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>route</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>source_reference</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>source_section</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>site_scope</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>security_scope</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>approval_status</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>effective_date</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>last_reviewed_date</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -542,7 +554,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QA-0018</t>
+          <t>KB-0095</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -552,50 +564,38 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Payment and Accounts Receivable Module</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Payments</t>
-        </is>
-      </c>
+          <t>Payment and Accounts Receivable Module</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>HELP_GENERIC</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>definition</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>What is a Payment?</t>
+          <t>What does Accounts Receivable track in SyteLine?</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>A Payment is the amount a customer remits against one or more Invoices, recorded to reduce their outstanding Receivable balance.</t>
+          <t>Accounts Receivable tracks posted customer invoices, credit and debit memos, payments, open items, and aging. The customer balance and invoice paid status are live financial facts and must be read from authorized current SyteLine records.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>payment,remittance</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>remittance,receipt</t>
-        </is>
-      </c>
+          <t>accounts receivable, invoices, payments, open items, customer balance</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>FAST_QA</t>
@@ -603,18 +603,16 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PTC Training Guide</t>
+          <t>payment.md</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+          <t>Payment and Accounts Receivable Module &gt; What A/R tracks</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -627,10 +625,14 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V2" t="b">
@@ -638,7 +640,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -650,7 +652,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QA-0008</t>
+          <t>KB-0096</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -660,50 +662,38 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Payment and Accounts Receivable Module</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Receivables</t>
-        </is>
-      </c>
+          <t>Payment and Accounts Receivable Module</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>HELP_GENERIC</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>definition</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>What is a Receivable?</t>
+          <t>Does a shipment or order status mean an invoice is settled in A/R?</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>A Receivable is the amount a customer still owes for goods or services already invoiced but not yet paid.</t>
+          <t>A shipment, an invoice, and a payment are separate events. Payment settles A/R items; order or shipment status alone does not prove settlement.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>receivable,outstanding balance</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>amount owed,outstanding balance</t>
-        </is>
-      </c>
+          <t>payment, shipment, invoice, settlement, accounts receivable</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>FAST_QA</t>
@@ -711,18 +701,16 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>PTC Training Guide</t>
+          <t>payment.md</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+          <t>Payment and Accounts Receivable Module &gt; What A/R tracks</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -735,10 +723,14 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V3" t="b">
@@ -746,10 +738,598 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KB-0097</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Payment and Accounts Receivable Module</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Payment and Accounts Receivable Module</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>How do I record and apply a customer payment in Accounts Receivable?</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Identify the customer, payment type/number, amount, currency, receipt date, and bank or cash context under local controls. Enter the payment on A/R Payments or use A/R Quick Payment Application if available, select the open invoice(s), credit(s), or finance charge(s) to settle, review distributions and discounts, then save and post with authorized A/R processing and verify the posted payment and remaining open balance.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>A/R Payments, customer payment, apply payment, payment distribution</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>payment.md</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Payment and Accounts Receivable Module &gt; Record and apply a customer payment</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0098</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Payment and Accounts Receivable Module</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Payment and Accounts Receivable Module</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>What should I do if a customer payment is unapplied?</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>For an unapplied payment, investigate remittance details and apply it later through the approved A/R process.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>unapplied payment, remittance, A/R process</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>payment.md</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Payment and Accounts Receivable Module &gt; Record and apply a customer payment</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0099</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Payment and Accounts Receivable Module</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Payment and Accounts Receivable Module</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HELP_GENERIC</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>What does the A/R Aging Report show and how is it used?</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>The A/R Aging Report groups open balances into configurable aging buckets and can show detailed open items or customer summaries. It is used for reviewing open receivables as of selected criteria, and its results may be used for customer statements and collection follow-up.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>A/R Aging Report, aging buckets, collections, statement</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>payment.md</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Payment and Accounts Receivable Module &gt; Aging and collections review</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0100</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Payment and Accounts Receivable Module</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Payment and Accounts Receivable Module</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>How do I run the A/R Aging Report correctly?</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Run the A/R Aging Report with the right as-of date, customer, currency, and site context; a past-due label depends on these options and billing terms.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>A/R Aging Report, as-of date, customer, billing terms</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>payment.md</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Payment and Accounts Receivable Module &gt; Aging and collections review</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KB-0101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Payment and Accounts Receivable Module</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Payment and Accounts Receivable Module</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>How do I troubleshoot when a customer says they paid but the invoice shows unpaid?</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>If a customer says they paid, look for the payment in A/R, confirm its posting status and customer, inspect distributions against the invoice, and check whether it remains open or was applied to another item.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>payment not applied, unpaid invoice, missing payment, A/R discrepancy</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>payment.md</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Payment and Accounts Receivable Module &gt; Troubleshoot unpaid or unmatched items</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KB-0102</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Payment and Accounts Receivable Module</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Payment and Accounts Receivable Module</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>What should I do if a payment amount doesn't match the invoice?</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>If a payment amount differs, inspect partial application, credits, discounts, currency, and bank reference.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>payment not applied, unpaid invoice, missing payment, A/R discrepancy</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>payment.md</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Payment and Accounts Receivable Module &gt; Troubleshoot unpaid or unmatched items</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -766,39 +1346,759 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>variation_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>question_variation</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>validated</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>KB-0095</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>What info does A/R keep track of?</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KB-0095</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Which items are monitored by Accounts Receivable?</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KB-0095</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>What does the A/R module record?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0096</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Does shipping an order mean it's paid in A/R?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0096</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Is an invoice settled when the order ships?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0096</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Does order status show if payment is done?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KB-0097</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>What are the steps to apply a customer payment?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KB-0097</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>How can I enter and post a payment from a customer?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KB-0097</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>What's the process for recording a payment in A/R?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KB-0098</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>How do I handle an unapplied payment?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KB-0098</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>What if a payment isn't applied to any invoice?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KB-0098</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Steps for dealing with unapplied customer payments?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KB-0099</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>What is the purpose of the A/R Aging Report?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KB-0099</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>How do I use the A/R Aging Report for collections?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KB-0099</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>What information does the A/R Aging Report provide?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KB-0100</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>What options should I select when running the A/R Aging Report?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KB-0100</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>How do I set up the A/R Aging Report for accurate results?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KB-0100</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Which criteria affect the A/R Aging Report output?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>KB-0101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>What should I check if a customer claims they paid but the invoice is still open?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KB-0101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Steps to find out why a payment isn't matched to an invoice?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>KB-0101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>How do I handle a missing payment in accounts receivable?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KB-0102</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>How do I resolve a payment amount mismatch?</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>KB-0102</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>What to check if the payment doesn't match the invoice total?</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>KB-0102</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Steps for handling partial or incorrect payments?</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
